--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/23 18:37:21</t>
+          <t>06/24 12:06:55</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>39506.17</t>
+          <t>24691.36</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -215,7 +215,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>200000</t>
         </is>
       </c>
     </row>
@@ -227,7 +227,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>39506.17</t>
+          <t>24691.36</t>
         </is>
       </c>
     </row>
@@ -251,7 +251,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>39506.17</t>
+          <t>24691.36</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>06/24 12:35:27</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>180000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.15</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>22085.89</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>06/24 12:06:55</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>24691.36</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>yxhgq52</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>200000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>380000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>46777.25</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>24691.36</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>46777.25</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/24 12:35:27</t>
+          <t>06/24 12:43:07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>22085.89</t>
+          <t>35714.29</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,183 +117,225 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>06/24 12:35:27</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>180000</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>8.15</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>22085.89</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>06/24 12:06:55</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>24691.36</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>yxhgq52</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>380000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>46777.25</t>
+          <t>680000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>82491.53</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>46777.25</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>82491.53</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -283,59 +283,86 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>06/24 12:43:13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>680000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>82491.53</t>
+          <t>680000</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>82491.53</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>82491.53</t>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>81903.53</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>06/25 16:32:57</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>400000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>49382.72</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>06/25 13:05:59</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>39506.17</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>yxhgq52</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>320000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>39506.17</t>
+          <t>720000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>88888.89</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>39506.17</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>88888.89</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/25 16:32:57</t>
+          <t>06/26 08:47:43</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>49382.72</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -114,186 +114,144 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>06/25 13:05:59</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>320000</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>8.1</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>39506.17</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>300000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>720000</t>
+          <t>37037.04</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>88888.89</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>88888.89</t>
+          <t>37037.04</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>06/26 10:00:12</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>19753.09</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>06/26 08:47:43</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>300000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>37037.04</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>yxhgq52</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>300000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>460000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>56790.12</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>37037.04</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>56790.12</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/26 10:00:12</t>
+          <t>06/26 14:39:57</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>19753.09</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,183 +117,225 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>06/26 10:00:12</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>19753.09</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>06/26 08:47:43</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>300000</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>37037.04</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>yxhgq52</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>460000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>56790.12</t>
+          <t>560000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>69135.8</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>56790.12</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>69135.8</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/27 11:40:49</t>
+          <t>06/29 12:46:01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>24844.72</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -215,7 +215,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
     </row>
@@ -227,7 +227,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>24844.72</t>
         </is>
       </c>
     </row>
@@ -251,7 +251,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>24844.72</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/29 12:46:01</t>
+          <t>06/30 10:05:33</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>24844.72</t>
+          <t>62111.8</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -215,7 +215,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -227,7 +227,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>24844.72</t>
+          <t>62111.8</t>
         </is>
       </c>
     </row>
@@ -251,7 +251,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>24844.72</t>
+          <t>62111.8</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>06/30 10:21:46</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>940000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>117500</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>06/30 10:05:33</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>500000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.05</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>62111.8</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>yxhgq52</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>500000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>62111.8</t>
+          <t>1440000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>179611.8</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>62111.8</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>179611.8</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/30 10:21:46</t>
+          <t>06/30 10:46:18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>117500</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,183 +117,225 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>06/30 10:21:46</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>940000</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>117500</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>06/30 10:05:33</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>500000</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>8.05</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>62111.8</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>yxhgq52</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1440000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>179611.8</t>
+          <t>1720000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>214179.7</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>179611.8</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>214179.7</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -283,59 +283,86 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>06/30 10:52:45</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1720000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>214179.7</t>
+          <t>1720000</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>214179.7</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>214179.7</t>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>214129.7</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -283,86 +283,59 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>06/30 10:52:45</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1720000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1720000</t>
+          <t>214179.7</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>214179.7</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>214129.7</t>
+          <t>214179.7</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/30 10:46:18</t>
+          <t>06/30 12:59:36</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>39751.55</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06/30 10:21:46</t>
+          <t>06/30 10:46:18</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>117500</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,183 +159,225 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>06/30 10:21:46</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>940000</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>117500</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>06/30 10:05:33</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>500000</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>8.05</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>62111.8</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>yxhgq52</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1720000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>214179.7</t>
+          <t>2040000</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>253931.26</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>214179.7</t>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>253931.26</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/30 12:59:36</t>
+          <t>06/30 13:54:27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>39751.55</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06/30 10:46:18</t>
+          <t>06/30 12:59:36</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>39751.55</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>06/30 10:21:46</t>
+          <t>06/30 10:46:18</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>117500</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,183 +201,225 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>06/30 10:21:46</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>940000</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>117500</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>06/30 10:05:33</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>500000</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>8.05</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>62111.8</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>yxhgq52</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2040000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>253931.26</t>
+          <t>2320000</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>288499.16</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>253931.26</t>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>288499.16</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/30 13:54:27</t>
+          <t>06/30 14:28:35</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06/30 12:59:36</t>
+          <t>06/30 13:54:27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>39751.55</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>06/30 10:46:18</t>
+          <t>06/30 12:59:36</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>39751.55</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>06/30 10:21:46</t>
+          <t>06/30 10:46:18</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>117500</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,183 +243,225 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>06/30 10:21:46</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>940000</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>117500</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>06/30 10:05:33</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>500000</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t>8.05</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>62111.8</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2320000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>288499.16</t>
+          <t>2420000</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>300769.1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>288499.16</t>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>300769.1</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/30 14:28:35</t>
+          <t>06/30 14:51:25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>18518.52</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06/30 13:54:27</t>
+          <t>06/30 14:28:35</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>06/30 12:59:36</t>
+          <t>06/30 13:54:27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>39751.55</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>06/30 10:46:18</t>
+          <t>06/30 12:59:36</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>39751.55</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>06/30 10:21:46</t>
+          <t>06/30 10:46:18</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>117500</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,183 +285,225 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>06/30 10:21:46</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>940000</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>117500</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>06/30 10:05:33</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>500000</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>8.05</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>62111.8</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2420000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>300769.1</t>
+          <t>2570000</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>319287.61</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>300769.1</t>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>319287.61</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -451,59 +451,86 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>06/30 14:52:47</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2570000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>319287.61</t>
+          <t>2570000</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>319287.61</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>319287.61</t>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>319099.61</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/30 14:51:25</t>
+          <t>06/30 18:54:28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>18518.52</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06/30 14:28:35</t>
+          <t>06/30 14:51:25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>18518.52</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>06/30 13:54:27</t>
+          <t>06/30 14:28:35</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>06/30 12:59:36</t>
+          <t>06/30 13:54:27</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>39751.55</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>06/30 10:46:18</t>
+          <t>06/30 12:59:36</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>39751.55</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>06/30 10:21:46</t>
+          <t>06/30 10:46:18</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>117500</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,210 +327,252 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>06/30 10:21:46</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>940000</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>117500</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>06/30 10:05:33</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>500000</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
         <is>
           <t>8.05</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>62111.8</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>标记人</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>操作人</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>06/30 14:52:47</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>188</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2570000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>319287.61</t>
+          <t>2850000</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>354287.61</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>319099.61</t>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>354099.61</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>07/01 14:50:08</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>390000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>48148.15</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>07/01 11:37:27</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>100000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.2</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>12195.12</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>yxhgq52</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>100000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>490000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>60343.27</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>12195.12</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>60343.27</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/01 14:50:08</t>
+          <t>07/01 15:38:21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>48148.15</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,183 +117,225 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>07/01 14:50:08</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>390000</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>48148.15</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>07/01 11:37:27</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>100000</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>8.2</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>12195.12</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>yxhgq52</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>490000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>60343.27</t>
+          <t>740000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>91593.27</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>60343.27</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>91593.27</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/01 15:38:21</t>
+          <t>07/01 18:40:58</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,22 +90,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t/>
+          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/01 14:50:08</t>
+          <t>07/01 15:38:21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>48148.15</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,183 +159,225 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>07/01 14:50:08</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>390000</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>48148.15</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>07/01 11:37:27</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>100000</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>8.2</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>12195.12</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>yxhgq52</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>740000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>91593.27</t>
+          <t>739990</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>91583.27</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>91593.27</t>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>91583.27</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/01 18:40:58</t>
+          <t>07/02 09:16:59</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,22 +90,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>28750</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
+          <t/>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -114,129 +114,53 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>07/01 15:38:21</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>250000</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>31250</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/01 14:50:08</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>390000</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>8.1</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>48148.15</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t/>
+          <t>代付</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/01 11:37:27</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>费率</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>汇率</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>结算</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
@@ -244,7 +168,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>代付</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
@@ -261,30 +185,15 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>费率</t>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>汇率</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
-        <is>
-          <t>结算</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -294,90 +203,55 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>下发</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>时间</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
+          <t>230000</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>28750</t>
+        </is>
+      </c>
+    </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>739990</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>应下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>91583.27</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>91583.27</t>
+          <t>28750</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>07/02 09:58:18</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.05</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>12422.36</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>07/02 09:16:59</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>230000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>28750</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>yxhgq52</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>230000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>28750</t>
+          <t>330000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>41172.36</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>28750</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>41172.36</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/02 09:58:18</t>
+          <t>07/02 15:46:17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>1064400</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12422.36</t>
+          <t>133050</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,183 +117,225 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>07/02 09:58:18</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>8.05</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>12422.36</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>07/02 09:16:59</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>230000</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>28750</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>yxhgq52</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>330000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>41172.36</t>
+          <t>1394400</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>174222.36</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>41172.36</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>174222.36</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>07/03 20:29:40</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>-12</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>-12</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>上海浦东新区 明天上午11</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>17万 问</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>07/03 13:13:45</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>325000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>7.9</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>41139.24</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>yxhgq52</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>325000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>41139.24</t>
+          <t>324988</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>41127.24</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>41139.24</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>41127.24</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/03 20:29:40</t>
+          <t>07/06 16:38:27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,210 +90,168 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t/>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>17万 问</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>07/03 13:13:45</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>325000</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>7.9</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>41139.24</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
           <t/>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+    </row>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>324988</t>
+          <t>12269.94</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>41127.24</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>41127.24</t>
+          <t>12269.94</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/06 16:38:27</t>
+          <t>07/07 10:57:24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -215,7 +215,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -227,7 +227,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>60240.96</t>
         </is>
       </c>
     </row>
@@ -251,7 +251,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>60240.96</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>07/07 12:04:13</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>50000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.15</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>6134.97</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>07/07 10:57:24</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>500000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>60240.96</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>yxhgq52</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>500000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>550000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>66375.93</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>60240.96</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>66375.93</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -241,59 +241,86 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>07/07 12:04:32</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>550000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>66375.93</t>
+          <t>550000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>66375.93</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>66375.93</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>66099.93</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/07 12:04:13</t>
+          <t>07/07 17:03:42</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>6134.97</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,210 +117,252 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>07/07 12:04:13</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>50000</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>8.15</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>6134.97</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>07/07 10:57:24</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>500000</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>60240.96</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>yxhgq52</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>标记人</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>操作人</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>07/07 12:04:32</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>276</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>yxhgq52</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>550000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>66375.93</t>
+          <t>850000</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>103643.01</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>66099.93</t>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>103367.01</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>07/08 11:55:35</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1000000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.05</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>124223.6</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>07/08 11:27:56</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.35</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>23952.1</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>yxhgq52</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>200000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>23952.1</t>
+          <t>1200000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>148175.7</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>23952.1</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>148175.7</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/08 11:55:35</t>
+          <t>07/09 09:51:15</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>124223.6</t>
+          <t>6172.84</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -114,186 +114,144 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>07/08 11:27:56</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>200000</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>8.35</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>23952.1</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>50000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1200000</t>
+          <t>6172.84</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>148175.7</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>148175.7</t>
+          <t>6172.84</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>07/09 09:52:18</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>370000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.05</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>45962.73</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>07/09 09:51:15</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>50000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>6172.84</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>yxhgq52</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>50000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>6172.84</t>
+          <t>420000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>52135.57</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>6172.84</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>52135.57</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/09 09:52:18</t>
+          <t>07/09 09:52:57</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>45962.73</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,183 +117,225 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>07/09 09:52:18</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>370000</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>8.05</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>45962.73</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>07/09 09:51:15</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>50000</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>6172.84</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>yxhgq52</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>420000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>52135.57</t>
+          <t>520000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>64183.77</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>52135.57</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>64183.77</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -75,7 +75,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/09 09:52:57</t>
+          <t>07/09 20:44:16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/09 09:52:18</t>
+          <t>07/09 09:52:57</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>45962.73</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,183 +159,225 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>07/09 09:52:18</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>370000</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>8.05</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>45962.73</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>07/09 09:51:15</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>50000</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>6172.84</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>yxhgq52</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>520000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>64183.77</t>
+          <t>620000</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>76231.96</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>64183.77</t>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>76231.96</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -72,144 +72,186 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>07/10 13:24:33</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>259980</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.8</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>29543.18</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>259980</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29543.18</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>29543.18</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>07/10 13:44:44</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>12195.12</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>07/10 13:24:33</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>259980</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.8</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>29543.18</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>yxhgq52</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>259980</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>29543.18</t>
+          <t>359980</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>41738.3</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>29543.18</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>41738.3</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/10 13:44:44</t>
+          <t>07/10 14:54:56</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>36809.82</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,183 +117,225 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>07/10 13:44:44</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>12195.12</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>07/10 13:24:33</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>259980</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>8.8</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>29543.18</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>yxhgq52</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>359980</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>41738.3</t>
+          <t>659980</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>78548.12</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>41738.3</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>78548.12</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/12 14:43:07</t>
+          <t>07/13 10:45:12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>600000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>18404.91</t>
+          <t>75000</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -215,7 +215,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>600000</t>
         </is>
       </c>
     </row>
@@ -227,7 +227,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>18404.91</t>
+          <t>75000</t>
         </is>
       </c>
     </row>
@@ -251,7 +251,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>18404.91</t>
+          <t>75000</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>07/13 12:08:35</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>175000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>21341.46</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>07/13 10:45:12</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>600000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>75000</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>yxhgq52</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>600000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>75000</t>
+          <t>775000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>96341.46</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>75000</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>96341.46</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/13 12:08:35</t>
+          <t>07/13 13:36:47</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>175000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>21341.46</t>
+          <t>62500</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,183 +117,225 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>07/13 12:08:35</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>175000</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>21341.46</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>07/13 10:45:12</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>600000</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>75000</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>yxhgq52</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>775000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>96341.46</t>
+          <t>1275000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>158841.46</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>96341.46</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>158841.46</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/14 19:36:11</t>
+          <t>07/15 16:22:26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>28395.06</t>
+          <t>13496.93</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -215,7 +215,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>110000</t>
         </is>
       </c>
     </row>
@@ -227,7 +227,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>28395.06</t>
+          <t>13496.93</t>
         </is>
       </c>
     </row>
@@ -251,7 +251,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>28395.06</t>
+          <t>13496.93</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>07/15 19:20:32</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>62500</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>07/15 16:22:26</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>110000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.15</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>13496.93</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>yxhgq52</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>110000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>13496.93</t>
+          <t>610000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>75996.93</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>13496.93</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>75996.93</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/15 19:20:32</t>
+          <t>07/16 12:19:58</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>62500</t>
+          <t>26190.48</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -114,186 +114,144 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>07/15 16:22:26</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>110000</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>8.15</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>13496.93</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>220000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>610000</t>
+          <t>26190.48</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>75996.93</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>75996.93</t>
+          <t>26190.48</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/16 12:19:58</t>
+          <t>07/17 10:45:36</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>120989</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.85</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>26190.48</t>
+          <t>13671.07</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -215,7 +215,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>120989</t>
         </is>
       </c>
     </row>
@@ -227,7 +227,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>26190.48</t>
+          <t>13671.07</t>
         </is>
       </c>
     </row>
@@ -251,7 +251,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>26190.48</t>
+          <t>13671.07</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>07/17 15:25:18</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.15</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>12269.94</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>07/17 10:45:36</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>120989</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.85</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>13671.07</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>yxhgq52</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>120989</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>13671.07</t>
+          <t>220989</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25941.01</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>13671.07</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>25941.01</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/17 15:25:18</t>
+          <t>07/17 17:10:27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,183 +117,225 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>07/17 15:25:18</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>8.15</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>12269.94</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>07/17 10:45:36</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>120989</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>8.85</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>13671.07</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>yxhgq52</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>220989</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>25941.01</t>
+          <t>470989</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>57191.01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>25941.01</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>57191.01</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/17 17:10:27</t>
+          <t>07/17 18:14:47</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>183843</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>22557.42</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/17 15:25:18</t>
+          <t>07/17 17:10:27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,183 +159,225 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>07/17 15:25:18</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>8.15</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>12269.94</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>07/17 10:45:36</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>120989</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>8.85</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>13671.07</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>yxhgq52</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>470989</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>57191.01</t>
+          <t>654832</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>79748.44</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>57191.01</t>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>79748.44</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/17 18:14:47</t>
+          <t>07/17 18:38:51</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>183843</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>22557.42</t>
+          <t>46250</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/17 17:10:27</t>
+          <t>07/17 18:14:47</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>183843</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>22557.42</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/17 15:25:18</t>
+          <t>07/17 17:10:27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,183 +201,225 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>07/17 15:25:18</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>8.15</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>12269.94</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>07/17 10:45:36</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>120989</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>8.85</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>13671.07</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>yxhgq52</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>654832</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>79748.44</t>
+          <t>1024832</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>125998.44</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>79748.44</t>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>125998.44</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/19 19:17:33</t>
+          <t>07/20 13:58:56</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>7361.96</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -215,7 +215,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>60000</t>
         </is>
       </c>
     </row>
@@ -227,7 +227,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>7361.96</t>
         </is>
       </c>
     </row>
@@ -251,7 +251,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>7361.96</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>07/20 14:01:29</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>438</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>60000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>7361.96</t>
+          <t>60000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7361.96</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>438</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>7361.96</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>6923.96</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/20 13:58:56</t>
+          <t>07/21 14:22:59</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>7361.96</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>07/20 14:01:29</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>438</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>12269.94</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>7361.96</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>438</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>6923.96</t>
+          <t>12269.94</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/21 14:22:59</t>
+          <t>07/22 10:20:48</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>7.95</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>25157.23</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -215,7 +215,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>200000</t>
         </is>
       </c>
     </row>
@@ -227,7 +227,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>25157.23</t>
         </is>
       </c>
     </row>
@@ -251,7 +251,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>25157.23</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>07/22 14:46:31</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>274950</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>33530.49</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>07/22 10:20:48</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>7.95</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>25157.23</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>yxhgq52</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>200000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>25157.23</t>
+          <t>474950</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>58687.72</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>25157.23</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>58687.72</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/22 14:46:31</t>
+          <t>07/22 14:50:27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>274950</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>33530.49</t>
+          <t>9638.55</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,183 +117,225 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>07/22 14:46:31</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>274950</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>33530.49</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>07/22 10:20:48</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>7.95</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>25157.23</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>yxhgq52</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>474950</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>58687.72</t>
+          <t>554950</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>68326.27</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>58687.72</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>68326.27</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>07/23 10:04:03</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>400000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>7.95</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>50314.47</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>07/23 09:57:25</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>420000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>52500</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>yxhgq52</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>420000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>52500</t>
+          <t>820000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>102814.47</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>52500</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>102814.47</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/23 10:04:03</t>
+          <t>07/23 10:46:36</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.95</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>50314.47</t>
+          <t>30864.2</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,183 +117,225 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>07/23 10:04:03</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>400000</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>7.95</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>50314.47</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>07/23 09:57:25</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>420000</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>52500</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>yxhgq52</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>820000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>102814.47</t>
+          <t>1070000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>133678.66</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>102814.47</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>133678.66</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>07/24 11:18:18</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>170000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>7.95</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>21383.65</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>07/24 10:09:54</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>130000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>15662.65</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>yxhgq52</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>130000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>15662.65</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>37046.3</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>15662.65</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>37046.3</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/24 11:18:18</t>
+          <t>07/25 14:40:44</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.95</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>21383.65</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -114,186 +114,144 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>07/24 10:09:54</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>130000</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>8.3</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>15662.65</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>12345.68</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>37046.3</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>37046.3</t>
+          <t>12345.68</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -75,7 +75,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/25 14:40:44</t>
+          <t>07/26 12:04:38</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -227,7 +227,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>12195.12</t>
         </is>
       </c>
     </row>
@@ -251,7 +251,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>12195.12</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>07/26 12:04:42</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>100000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12195.12</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>12195.12</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>11807.12</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -72,213 +72,144 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>07/26 12:04:38</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>100000</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>8.2</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>12195.12</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="6"/>
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/26 12:04:42</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>388</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12195.12</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>388</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>11807.12</t>
+          <t>0</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -72,144 +72,186 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>07/27 10:20:29</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>290000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.05</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>36024.84</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>yxhgq79</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>290000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>36024.84</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>36024.84</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/27 10:20:29</t>
+          <t>07/28 12:19:44</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>290000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>36024.84</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>yxhgq79</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -215,7 +215,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>290000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -227,7 +227,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>36024.84</t>
+          <t>12269.94</t>
         </is>
       </c>
     </row>
@@ -251,7 +251,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>36024.84</t>
+          <t>12269.94</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/28 12:19:44</t>
+          <t>07/29 20:09:55</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>185000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>22699.39</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -215,7 +215,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>185000</t>
         </is>
       </c>
     </row>
@@ -227,7 +227,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>22699.39</t>
         </is>
       </c>
     </row>
@@ -251,7 +251,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>22699.39</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/29 20:09:55</t>
+          <t>07/31 14:43:55</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>185000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>22699.39</t>
+          <t>20987.65</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -215,7 +215,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>185000</t>
+          <t>170000</t>
         </is>
       </c>
     </row>
@@ -227,7 +227,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>22699.39</t>
+          <t>20987.65</t>
         </is>
       </c>
     </row>
@@ -251,7 +251,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>22699.39</t>
+          <t>20987.65</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>07/31 14:54:55</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>350000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>7.95</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>44025.16</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>07/31 14:43:55</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>170000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>20987.65</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>yxhgq52</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>170000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>20987.65</t>
+          <t>520000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>65012.81</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>20987.65</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>65012.81</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/31 14:54:55</t>
+          <t>07/31 20:07:18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>350000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.95</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>44025.16</t>
+          <t>18750</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,183 +117,225 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>07/31 14:54:55</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>350000</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>7.95</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>44025.16</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>07/31 14:43:55</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>170000</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>20987.65</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>yxhgq52</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>520000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>65012.81</t>
+          <t>670000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>83762.81</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>65012.81</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>83762.81</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>08/04 15:44:12</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>12500</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>08/04 13:42:03</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>100000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.15</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>12269.94</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>yxhgq52</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>100000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>200000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24769.94</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>12269.94</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>24769.94</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/04 15:44:12</t>
+          <t>08/07 10:14:02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.95</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12500</t>
+          <t>37735.85</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -114,186 +114,144 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>08/04 13:42:03</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>100000</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>8.15</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>12269.94</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>300000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>37735.85</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>24769.94</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>24769.94</t>
+          <t>37735.85</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>08/07 13:36:26</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>250000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>30864.2</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>08/07 10:14:02</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>300000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>7.95</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>37735.85</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>yxhgq52</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>300000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>37735.85</t>
+          <t>550000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>68600.05</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>37735.85</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>68600.05</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -75,7 +75,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/07 13:36:26</t>
+          <t>08/07 20:48:29</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>30864.2</t>
+          <t>31645.57</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,183 +117,225 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>08/07 13:36:26</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>250000</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>30864.2</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>08/07 10:14:02</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>300000</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>7.95</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>37735.85</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>yxhgq52</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>550000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>68600.05</t>
+          <t>800000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>100245.62</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>68600.05</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>100245.62</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/10 14:50:45</t>
+          <t>08/11 14:11:45</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1020000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.85</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>129936.31</t>
+          <t>10975.61</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -215,7 +215,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1020000</t>
+          <t>90000</t>
         </is>
       </c>
     </row>
@@ -227,7 +227,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>129936.31</t>
+          <t>10975.61</t>
         </is>
       </c>
     </row>
@@ -251,7 +251,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>129936.31</t>
+          <t>10975.61</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/11 14:11:45</t>
+          <t>08/13 16:30:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>10975.61</t>
+          <t>17283.95</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -215,7 +215,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>140000</t>
         </is>
       </c>
     </row>
@@ -227,7 +227,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>10975.61</t>
+          <t>17283.95</t>
         </is>
       </c>
     </row>
@@ -251,7 +251,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>10975.61</t>
+          <t>17283.95</t>
         </is>
       </c>
     </row>
